--- a/selenium-tests/selenium-tests/reports/selenium-report.xlsx
+++ b/selenium-tests/selenium-tests/reports/selenium-report.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="848" uniqueCount="378">
   <si>
     <t>Test ID</t>
   </si>
@@ -35,13 +35,1125 @@
   </si>
   <si>
     <t>Screenshot Path</t>
+  </si>
+  <si>
+    <t>TC_061</t>
+  </si>
+  <si>
+    <t>Ticket creation modal render test 61</t>
+  </si>
+  <si>
+    <t>Tickets</t>
+  </si>
+  <si>
+    <t>PASS</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>2026-08-11T05:08:31.461Z</t>
+  </si>
+  <si>
+    <t>TC_062</t>
+  </si>
+  <si>
+    <t>Ticket creation modal render test 62</t>
+  </si>
+  <si>
+    <t>2026-08-11T05:08:43.158Z</t>
+  </si>
+  <si>
+    <t>TC_063</t>
+  </si>
+  <si>
+    <t>Ticket creation modal render test 63</t>
+  </si>
+  <si>
+    <t>2026-08-11T05:08:55.034Z</t>
+  </si>
+  <si>
+    <t>TC_064</t>
+  </si>
+  <si>
+    <t>Ticket creation modal render test 64</t>
+  </si>
+  <si>
+    <t>2026-08-11T05:09:06.121Z</t>
+  </si>
+  <si>
+    <t>TC_065</t>
+  </si>
+  <si>
+    <t>Ticket creation modal render test 65</t>
+  </si>
+  <si>
+    <t>2026-08-11T05:09:18.243Z</t>
+  </si>
+  <si>
+    <t>TC_066</t>
+  </si>
+  <si>
+    <t>Ticket creation modal render test 66</t>
+  </si>
+  <si>
+    <t>2026-08-11T05:09:28.828Z</t>
+  </si>
+  <si>
+    <t>TC_067</t>
+  </si>
+  <si>
+    <t>Ticket creation modal render test 67</t>
+  </si>
+  <si>
+    <t>2026-08-11T05:09:38.871Z</t>
+  </si>
+  <si>
+    <t>TC_068</t>
+  </si>
+  <si>
+    <t>Ticket creation modal render test 68</t>
+  </si>
+  <si>
+    <t>2026-08-11T05:09:49.503Z</t>
+  </si>
+  <si>
+    <t>TC_069</t>
+  </si>
+  <si>
+    <t>Ticket creation modal render test 69</t>
+  </si>
+  <si>
+    <t>2026-08-11T05:09:59.169Z</t>
+  </si>
+  <si>
+    <t>TC_070</t>
+  </si>
+  <si>
+    <t>Ticket creation modal render test 70</t>
+  </si>
+  <si>
+    <t>2026-08-11T05:10:06.372Z</t>
+  </si>
+  <si>
+    <t>TC_071</t>
+  </si>
+  <si>
+    <t>Ticket creation modal render test 71</t>
+  </si>
+  <si>
+    <t>2026-08-11T05:10:16.397Z</t>
+  </si>
+  <si>
+    <t>TC_072</t>
+  </si>
+  <si>
+    <t>Ticket creation modal render test 72</t>
+  </si>
+  <si>
+    <t>2026-08-11T05:10:28.925Z</t>
+  </si>
+  <si>
+    <t>TC_073</t>
+  </si>
+  <si>
+    <t>Ticket creation modal render test 73</t>
+  </si>
+  <si>
+    <t>2026-08-11T05:10:38.674Z</t>
+  </si>
+  <si>
+    <t>TC_074</t>
+  </si>
+  <si>
+    <t>Ticket creation modal render test 74</t>
+  </si>
+  <si>
+    <t>2026-08-11T05:10:48.887Z</t>
+  </si>
+  <si>
+    <t>TC_075</t>
+  </si>
+  <si>
+    <t>Ticket creation modal render test 75</t>
+  </si>
+  <si>
+    <t>2026-08-11T05:11:00.469Z</t>
+  </si>
+  <si>
+    <t>TC_076</t>
+  </si>
+  <si>
+    <t>Kanban board column test 76</t>
+  </si>
+  <si>
+    <t>Kanban</t>
+  </si>
+  <si>
+    <t>2026-08-11T05:11:13.888Z</t>
+  </si>
+  <si>
+    <t>TC_077</t>
+  </si>
+  <si>
+    <t>Kanban board column test 77</t>
+  </si>
+  <si>
+    <t>2026-08-11T05:11:27.720Z</t>
+  </si>
+  <si>
+    <t>TC_078</t>
+  </si>
+  <si>
+    <t>Kanban board column test 78</t>
+  </si>
+  <si>
+    <t>2026-08-11T05:11:42.705Z</t>
+  </si>
+  <si>
+    <t>TC_079</t>
+  </si>
+  <si>
+    <t>Kanban board column test 79</t>
+  </si>
+  <si>
+    <t>2026-08-11T05:11:56.871Z</t>
+  </si>
+  <si>
+    <t>TC_080</t>
+  </si>
+  <si>
+    <t>Kanban board column test 80</t>
+  </si>
+  <si>
+    <t>2026-08-11T05:12:14.611Z</t>
+  </si>
+  <si>
+    <t>TC_081</t>
+  </si>
+  <si>
+    <t>Kanban board column test 81</t>
+  </si>
+  <si>
+    <t>2026-08-11T05:12:31.015Z</t>
+  </si>
+  <si>
+    <t>TC_082</t>
+  </si>
+  <si>
+    <t>Kanban board column test 82</t>
+  </si>
+  <si>
+    <t>2026-08-11T05:12:49.505Z</t>
+  </si>
+  <si>
+    <t>TC_083</t>
+  </si>
+  <si>
+    <t>Kanban board column test 83</t>
+  </si>
+  <si>
+    <t>2026-08-11T05:13:00.974Z</t>
+  </si>
+  <si>
+    <t>TC_084</t>
+  </si>
+  <si>
+    <t>Kanban board column test 84</t>
+  </si>
+  <si>
+    <t>2026-08-11T05:13:15.491Z</t>
+  </si>
+  <si>
+    <t>TC_085</t>
+  </si>
+  <si>
+    <t>Kanban board column test 85</t>
+  </si>
+  <si>
+    <t>2026-08-11T05:13:29.820Z</t>
+  </si>
+  <si>
+    <t>TC_086</t>
+  </si>
+  <si>
+    <t>Kanban board column test 86</t>
+  </si>
+  <si>
+    <t>2026-08-11T05:13:43.948Z</t>
+  </si>
+  <si>
+    <t>TC_087</t>
+  </si>
+  <si>
+    <t>Kanban board column test 87</t>
+  </si>
+  <si>
+    <t>2026-08-11T05:13:50.170Z</t>
+  </si>
+  <si>
+    <t>TC_088</t>
+  </si>
+  <si>
+    <t>Kanban board column test 88</t>
+  </si>
+  <si>
+    <t>2026-08-11T05:14:01.429Z</t>
+  </si>
+  <si>
+    <t>TC_089</t>
+  </si>
+  <si>
+    <t>Kanban board column test 89</t>
+  </si>
+  <si>
+    <t>2026-08-11T05:14:07.526Z</t>
+  </si>
+  <si>
+    <t>TC_090</t>
+  </si>
+  <si>
+    <t>Kanban board column test 90</t>
+  </si>
+  <si>
+    <t>2026-08-11T05:14:17.543Z</t>
+  </si>
+  <si>
+    <t>TC_091</t>
+  </si>
+  <si>
+    <t>Ticket details test 91</t>
+  </si>
+  <si>
+    <t>2026-08-11T05:14:25.566Z</t>
+  </si>
+  <si>
+    <t>TC_092</t>
+  </si>
+  <si>
+    <t>Ticket details test 92</t>
+  </si>
+  <si>
+    <t>2026-08-11T05:14:32.396Z</t>
+  </si>
+  <si>
+    <t>TC_093</t>
+  </si>
+  <si>
+    <t>Ticket details test 93</t>
+  </si>
+  <si>
+    <t>2026-08-11T05:14:43.185Z</t>
+  </si>
+  <si>
+    <t>TC_094</t>
+  </si>
+  <si>
+    <t>Ticket details test 94</t>
+  </si>
+  <si>
+    <t>2026-08-11T05:14:51.397Z</t>
+  </si>
+  <si>
+    <t>TC_095</t>
+  </si>
+  <si>
+    <t>Ticket details test 95</t>
+  </si>
+  <si>
+    <t>2026-08-11T05:15:02.911Z</t>
+  </si>
+  <si>
+    <t>TC_096</t>
+  </si>
+  <si>
+    <t>Ticket details test 96</t>
+  </si>
+  <si>
+    <t>2026-08-11T05:15:13.082Z</t>
+  </si>
+  <si>
+    <t>TC_097</t>
+  </si>
+  <si>
+    <t>Ticket details test 97</t>
+  </si>
+  <si>
+    <t>2026-08-11T05:15:21.098Z</t>
+  </si>
+  <si>
+    <t>TC_098</t>
+  </si>
+  <si>
+    <t>Ticket details test 98</t>
+  </si>
+  <si>
+    <t>2026-08-11T05:15:28.924Z</t>
+  </si>
+  <si>
+    <t>TC_099</t>
+  </si>
+  <si>
+    <t>Ticket details test 99</t>
+  </si>
+  <si>
+    <t>2026-08-11T05:15:39.256Z</t>
+  </si>
+  <si>
+    <t>TC_100</t>
+  </si>
+  <si>
+    <t>Ticket details test 100</t>
+  </si>
+  <si>
+    <t>2026-08-11T05:15:47.153Z</t>
+  </si>
+  <si>
+    <t>TC_101</t>
+  </si>
+  <si>
+    <t>Ticket details test 101</t>
+  </si>
+  <si>
+    <t>2026-08-11T05:15:58.305Z</t>
+  </si>
+  <si>
+    <t>TC_102</t>
+  </si>
+  <si>
+    <t>Ticket details test 102</t>
+  </si>
+  <si>
+    <t>2026-08-11T05:16:05.415Z</t>
+  </si>
+  <si>
+    <t>TC_103</t>
+  </si>
+  <si>
+    <t>Ticket details test 103</t>
+  </si>
+  <si>
+    <t>2026-08-11T05:16:15.158Z</t>
+  </si>
+  <si>
+    <t>TC_104</t>
+  </si>
+  <si>
+    <t>Ticket details test 104</t>
+  </si>
+  <si>
+    <t>2026-08-11T05:16:25.254Z</t>
+  </si>
+  <si>
+    <t>TC_105</t>
+  </si>
+  <si>
+    <t>Ticket details test 105</t>
+  </si>
+  <si>
+    <t>2026-08-11T05:16:39.115Z</t>
+  </si>
+  <si>
+    <t>TC_106</t>
+  </si>
+  <si>
+    <t>Ticket search filter test 106</t>
+  </si>
+  <si>
+    <t>2026-08-11T05:16:45.987Z</t>
+  </si>
+  <si>
+    <t>TC_107</t>
+  </si>
+  <si>
+    <t>Ticket search filter test 107</t>
+  </si>
+  <si>
+    <t>2026-08-11T05:16:57.760Z</t>
+  </si>
+  <si>
+    <t>TC_108</t>
+  </si>
+  <si>
+    <t>Ticket search filter test 108</t>
+  </si>
+  <si>
+    <t>2026-08-11T05:17:08.040Z</t>
+  </si>
+  <si>
+    <t>TC_109</t>
+  </si>
+  <si>
+    <t>Ticket search filter test 109</t>
+  </si>
+  <si>
+    <t>2026-08-11T05:17:19.261Z</t>
+  </si>
+  <si>
+    <t>TC_110</t>
+  </si>
+  <si>
+    <t>Ticket search filter test 110</t>
+  </si>
+  <si>
+    <t>2026-08-11T05:17:29.868Z</t>
+  </si>
+  <si>
+    <t>TC_111</t>
+  </si>
+  <si>
+    <t>Ticket search filter test 111</t>
+  </si>
+  <si>
+    <t>2026-08-11T05:17:44.815Z</t>
+  </si>
+  <si>
+    <t>TC_112</t>
+  </si>
+  <si>
+    <t>Ticket search filter test 112</t>
+  </si>
+  <si>
+    <t>2026-08-11T05:17:57.025Z</t>
+  </si>
+  <si>
+    <t>TC_113</t>
+  </si>
+  <si>
+    <t>Ticket search filter test 113</t>
+  </si>
+  <si>
+    <t>2026-08-11T05:18:10.563Z</t>
+  </si>
+  <si>
+    <t>TC_114</t>
+  </si>
+  <si>
+    <t>Ticket search filter test 114</t>
+  </si>
+  <si>
+    <t>2026-08-11T05:18:19.544Z</t>
+  </si>
+  <si>
+    <t>TC_115</t>
+  </si>
+  <si>
+    <t>Ticket search filter test 115</t>
+  </si>
+  <si>
+    <t>2026-08-11T05:18:29.474Z</t>
+  </si>
+  <si>
+    <t>TC_116</t>
+  </si>
+  <si>
+    <t>Ticket search filter test 116</t>
+  </si>
+  <si>
+    <t>2026-08-11T05:18:35.074Z</t>
+  </si>
+  <si>
+    <t>TC_117</t>
+  </si>
+  <si>
+    <t>Ticket search filter test 117</t>
+  </si>
+  <si>
+    <t>2026-08-11T05:18:39.506Z</t>
+  </si>
+  <si>
+    <t>TC_118</t>
+  </si>
+  <si>
+    <t>Ticket search filter test 118</t>
+  </si>
+  <si>
+    <t>2026-08-11T05:18:44.008Z</t>
+  </si>
+  <si>
+    <t>TC_119</t>
+  </si>
+  <si>
+    <t>Ticket search filter test 119</t>
+  </si>
+  <si>
+    <t>2026-08-11T05:18:48.749Z</t>
+  </si>
+  <si>
+    <t>TC_120</t>
+  </si>
+  <si>
+    <t>Ticket search filter test 120</t>
+  </si>
+  <si>
+    <t>2026-08-11T05:18:53.152Z</t>
+  </si>
+  <si>
+    <t>TC_181</t>
+  </si>
+  <si>
+    <t>Profile form test 181</t>
+  </si>
+  <si>
+    <t>Profile</t>
+  </si>
+  <si>
+    <t>2026-08-11T05:07:40.143Z</t>
+  </si>
+  <si>
+    <t>TC_182</t>
+  </si>
+  <si>
+    <t>Profile form test 182</t>
+  </si>
+  <si>
+    <t>2026-08-11T05:07:46.470Z</t>
+  </si>
+  <si>
+    <t>TC_183</t>
+  </si>
+  <si>
+    <t>Profile form test 183</t>
+  </si>
+  <si>
+    <t>2026-08-11T05:07:53.614Z</t>
+  </si>
+  <si>
+    <t>TC_184</t>
+  </si>
+  <si>
+    <t>Profile form test 184</t>
+  </si>
+  <si>
+    <t>2026-08-11T05:08:01.452Z</t>
+  </si>
+  <si>
+    <t>TC_185</t>
+  </si>
+  <si>
+    <t>Profile form test 185</t>
+  </si>
+  <si>
+    <t>2026-08-11T05:08:09.005Z</t>
+  </si>
+  <si>
+    <t>TC_186</t>
+  </si>
+  <si>
+    <t>Profile form test 186</t>
+  </si>
+  <si>
+    <t>2026-08-11T05:08:19.827Z</t>
+  </si>
+  <si>
+    <t>TC_187</t>
+  </si>
+  <si>
+    <t>Profile form test 187</t>
+  </si>
+  <si>
+    <t>2026-08-11T05:08:31.895Z</t>
+  </si>
+  <si>
+    <t>TC_188</t>
+  </si>
+  <si>
+    <t>Profile form test 188</t>
+  </si>
+  <si>
+    <t>2026-08-11T05:08:43.847Z</t>
+  </si>
+  <si>
+    <t>TC_189</t>
+  </si>
+  <si>
+    <t>Profile form test 189</t>
+  </si>
+  <si>
+    <t>2026-08-11T05:08:56.294Z</t>
+  </si>
+  <si>
+    <t>TC_190</t>
+  </si>
+  <si>
+    <t>Profile form test 190</t>
+  </si>
+  <si>
+    <t>2026-08-11T05:09:09.627Z</t>
+  </si>
+  <si>
+    <t>TC_191</t>
+  </si>
+  <si>
+    <t>Profile form test 191</t>
+  </si>
+  <si>
+    <t>2026-08-11T05:09:22.625Z</t>
+  </si>
+  <si>
+    <t>TC_192</t>
+  </si>
+  <si>
+    <t>Profile form test 192</t>
+  </si>
+  <si>
+    <t>2026-08-11T05:09:32.876Z</t>
+  </si>
+  <si>
+    <t>TC_193</t>
+  </si>
+  <si>
+    <t>Profile form test 193</t>
+  </si>
+  <si>
+    <t>2026-08-11T05:09:43.357Z</t>
+  </si>
+  <si>
+    <t>TC_194</t>
+  </si>
+  <si>
+    <t>Profile form test 194</t>
+  </si>
+  <si>
+    <t>2026-08-11T05:09:54.760Z</t>
+  </si>
+  <si>
+    <t>TC_195</t>
+  </si>
+  <si>
+    <t>Profile form test 195</t>
+  </si>
+  <si>
+    <t>2026-08-11T05:10:03.088Z</t>
+  </si>
+  <si>
+    <t>TC_196</t>
+  </si>
+  <si>
+    <t>Settings theme toggle test 196</t>
+  </si>
+  <si>
+    <t>Settings</t>
+  </si>
+  <si>
+    <t>2026-08-11T05:10:12.013Z</t>
+  </si>
+  <si>
+    <t>TC_197</t>
+  </si>
+  <si>
+    <t>Settings theme toggle test 197</t>
+  </si>
+  <si>
+    <t>2026-08-11T05:10:23.485Z</t>
+  </si>
+  <si>
+    <t>TC_198</t>
+  </si>
+  <si>
+    <t>Settings theme toggle test 198</t>
+  </si>
+  <si>
+    <t>2026-08-11T05:10:33.516Z</t>
+  </si>
+  <si>
+    <t>TC_199</t>
+  </si>
+  <si>
+    <t>Settings theme toggle test 199</t>
+  </si>
+  <si>
+    <t>2026-08-11T05:10:41.867Z</t>
+  </si>
+  <si>
+    <t>TC_200</t>
+  </si>
+  <si>
+    <t>Settings theme toggle test 200</t>
+  </si>
+  <si>
+    <t>2026-08-11T05:10:52.944Z</t>
+  </si>
+  <si>
+    <t>TC_201</t>
+  </si>
+  <si>
+    <t>Settings theme toggle test 201</t>
+  </si>
+  <si>
+    <t>2026-08-11T05:11:04.855Z</t>
+  </si>
+  <si>
+    <t>TC_202</t>
+  </si>
+  <si>
+    <t>Settings theme toggle test 202</t>
+  </si>
+  <si>
+    <t>2026-08-11T05:11:15.333Z</t>
+  </si>
+  <si>
+    <t>TC_203</t>
+  </si>
+  <si>
+    <t>Settings theme toggle test 203</t>
+  </si>
+  <si>
+    <t>2026-08-11T05:11:27.862Z</t>
+  </si>
+  <si>
+    <t>TC_204</t>
+  </si>
+  <si>
+    <t>Settings theme toggle test 204</t>
+  </si>
+  <si>
+    <t>2026-08-11T05:11:42.567Z</t>
+  </si>
+  <si>
+    <t>TC_205</t>
+  </si>
+  <si>
+    <t>Settings theme toggle test 205</t>
+  </si>
+  <si>
+    <t>2026-08-11T05:11:57.928Z</t>
+  </si>
+  <si>
+    <t>TC_206</t>
+  </si>
+  <si>
+    <t>Settings theme toggle test 206</t>
+  </si>
+  <si>
+    <t>2026-08-11T05:12:14.982Z</t>
+  </si>
+  <si>
+    <t>TC_207</t>
+  </si>
+  <si>
+    <t>Settings theme toggle test 207</t>
+  </si>
+  <si>
+    <t>2026-08-11T05:12:33.341Z</t>
+  </si>
+  <si>
+    <t>TC_208</t>
+  </si>
+  <si>
+    <t>Settings theme toggle test 208</t>
+  </si>
+  <si>
+    <t>2026-08-11T05:12:52.198Z</t>
+  </si>
+  <si>
+    <t>TC_209</t>
+  </si>
+  <si>
+    <t>Settings theme toggle test 209</t>
+  </si>
+  <si>
+    <t>2026-08-11T05:13:09.566Z</t>
+  </si>
+  <si>
+    <t>TC_210</t>
+  </si>
+  <si>
+    <t>Settings theme toggle test 210</t>
+  </si>
+  <si>
+    <t>2026-08-11T05:13:29.696Z</t>
+  </si>
+  <si>
+    <t>TC_211</t>
+  </si>
+  <si>
+    <t>Sidebar navigation links test 211</t>
+  </si>
+  <si>
+    <t>Navigation</t>
+  </si>
+  <si>
+    <t>2026-08-11T05:13:43.898Z</t>
+  </si>
+  <si>
+    <t>TC_212</t>
+  </si>
+  <si>
+    <t>Sidebar navigation links test 212</t>
+  </si>
+  <si>
+    <t>2026-08-11T05:13:52.700Z</t>
+  </si>
+  <si>
+    <t>TC_213</t>
+  </si>
+  <si>
+    <t>Sidebar navigation links test 213</t>
+  </si>
+  <si>
+    <t>2026-08-11T05:14:00.732Z</t>
+  </si>
+  <si>
+    <t>TC_214</t>
+  </si>
+  <si>
+    <t>Sidebar navigation links test 214</t>
+  </si>
+  <si>
+    <t>2026-08-11T05:14:07.120Z</t>
+  </si>
+  <si>
+    <t>TC_215</t>
+  </si>
+  <si>
+    <t>Sidebar navigation links test 215</t>
+  </si>
+  <si>
+    <t>2026-08-11T05:14:14.017Z</t>
+  </si>
+  <si>
+    <t>TC_216</t>
+  </si>
+  <si>
+    <t>Sidebar navigation links test 216</t>
+  </si>
+  <si>
+    <t>2026-08-11T05:14:25.893Z</t>
+  </si>
+  <si>
+    <t>TC_217</t>
+  </si>
+  <si>
+    <t>Sidebar navigation links test 217</t>
+  </si>
+  <si>
+    <t>2026-08-11T05:14:36.837Z</t>
+  </si>
+  <si>
+    <t>TC_218</t>
+  </si>
+  <si>
+    <t>Sidebar navigation links test 218</t>
+  </si>
+  <si>
+    <t>2026-08-11T05:14:45.524Z</t>
+  </si>
+  <si>
+    <t>TC_219</t>
+  </si>
+  <si>
+    <t>Sidebar navigation links test 219</t>
+  </si>
+  <si>
+    <t>2026-08-11T05:14:53.103Z</t>
+  </si>
+  <si>
+    <t>TC_220</t>
+  </si>
+  <si>
+    <t>Sidebar navigation links test 220</t>
+  </si>
+  <si>
+    <t>2026-08-11T05:15:03.305Z</t>
+  </si>
+  <si>
+    <t>TC_221</t>
+  </si>
+  <si>
+    <t>Sidebar navigation links test 221</t>
+  </si>
+  <si>
+    <t>2026-08-11T05:15:13.166Z</t>
+  </si>
+  <si>
+    <t>TC_222</t>
+  </si>
+  <si>
+    <t>Sidebar navigation links test 222</t>
+  </si>
+  <si>
+    <t>2026-08-11T05:15:23.389Z</t>
+  </si>
+  <si>
+    <t>TC_223</t>
+  </si>
+  <si>
+    <t>Sidebar navigation links test 223</t>
+  </si>
+  <si>
+    <t>2026-08-11T05:15:33.131Z</t>
+  </si>
+  <si>
+    <t>TC_224</t>
+  </si>
+  <si>
+    <t>Sidebar navigation links test 224</t>
+  </si>
+  <si>
+    <t>2026-08-11T05:15:42.765Z</t>
+  </si>
+  <si>
+    <t>TC_225</t>
+  </si>
+  <si>
+    <t>Sidebar navigation links test 225</t>
+  </si>
+  <si>
+    <t>2026-08-11T05:15:50.947Z</t>
+  </si>
+  <si>
+    <t>TC_226</t>
+  </si>
+  <si>
+    <t>RBAC route guard test 226</t>
+  </si>
+  <si>
+    <t>RBAC</t>
+  </si>
+  <si>
+    <t>FAIL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">expect(received).not.toContain(expected) // indexOf
+Expected substring: not "/users"
+Received string:        "http://localhost:3000/users"</t>
+  </si>
+  <si>
+    <t>2026-08-11T05:15:59.554Z</t>
+  </si>
+  <si>
+    <t>TC_227</t>
+  </si>
+  <si>
+    <t>RBAC route guard test 227</t>
+  </si>
+  <si>
+    <t>2026-08-11T05:16:09.830Z</t>
+  </si>
+  <si>
+    <t>TC_228</t>
+  </si>
+  <si>
+    <t>RBAC route guard test 228</t>
+  </si>
+  <si>
+    <t>2026-08-11T05:16:18.391Z</t>
+  </si>
+  <si>
+    <t>TC_229</t>
+  </si>
+  <si>
+    <t>RBAC route guard test 229</t>
+  </si>
+  <si>
+    <t>2026-08-11T05:16:29.476Z</t>
+  </si>
+  <si>
+    <t>TC_230</t>
+  </si>
+  <si>
+    <t>RBAC route guard test 230</t>
+  </si>
+  <si>
+    <t>2026-08-11T05:16:39.916Z</t>
+  </si>
+  <si>
+    <t>TC_231</t>
+  </si>
+  <si>
+    <t>RBAC route guard test 231</t>
+  </si>
+  <si>
+    <t>2026-08-11T05:16:52.206Z</t>
+  </si>
+  <si>
+    <t>TC_232</t>
+  </si>
+  <si>
+    <t>RBAC route guard test 232</t>
+  </si>
+  <si>
+    <t>2026-08-11T05:17:03.634Z</t>
+  </si>
+  <si>
+    <t>TC_233</t>
+  </si>
+  <si>
+    <t>RBAC route guard test 233</t>
+  </si>
+  <si>
+    <t>2026-08-11T05:17:14.092Z</t>
+  </si>
+  <si>
+    <t>TC_234</t>
+  </si>
+  <si>
+    <t>RBAC route guard test 234</t>
+  </si>
+  <si>
+    <t>2026-08-11T05:17:28.156Z</t>
+  </si>
+  <si>
+    <t>TC_235</t>
+  </si>
+  <si>
+    <t>RBAC route guard test 235</t>
+  </si>
+  <si>
+    <t>2026-08-11T05:17:43.660Z</t>
+  </si>
+  <si>
+    <t>TC_236</t>
+  </si>
+  <si>
+    <t>RBAC route guard test 236</t>
+  </si>
+  <si>
+    <t>2026-08-11T05:17:55.029Z</t>
+  </si>
+  <si>
+    <t>TC_237</t>
+  </si>
+  <si>
+    <t>RBAC route guard test 237</t>
+  </si>
+  <si>
+    <t>2026-08-11T05:18:06.427Z</t>
+  </si>
+  <si>
+    <t>TC_238</t>
+  </si>
+  <si>
+    <t>RBAC route guard test 238</t>
+  </si>
+  <si>
+    <t>2026-08-11T05:18:16.476Z</t>
+  </si>
+  <si>
+    <t>TC_239</t>
+  </si>
+  <si>
+    <t>RBAC route guard test 239</t>
+  </si>
+  <si>
+    <t>2026-08-11T05:18:24.544Z</t>
+  </si>
+  <si>
+    <t>TC_240</t>
+  </si>
+  <si>
+    <t>RBAC route guard test 240</t>
+  </si>
+  <si>
+    <t>2026-08-11T05:18:34.233Z</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -53,8 +1165,16 @@
       <b/>
       <color rgb="FFFFFF"/>
     </font>
+    <font>
+      <b/>
+      <color rgb="166534"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="991B1B"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -64,6 +1184,16 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="1E293B"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="DCFCE7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FEE2E2"/>
       </patternFill>
     </fill>
   </fills>
@@ -79,9 +1209,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -421,7 +1553,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H121"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -460,6 +1592,3126 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F2">
+        <v>18667</v>
+      </c>
+      <c r="G2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F3">
+        <v>11677</v>
+      </c>
+      <c r="G3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F4">
+        <v>11871</v>
+      </c>
+      <c r="G4" t="s">
+        <v>19</v>
+      </c>
+      <c r="H4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>20</v>
+      </c>
+      <c r="B5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F5">
+        <v>11067</v>
+      </c>
+      <c r="G5" t="s">
+        <v>22</v>
+      </c>
+      <c r="H5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>23</v>
+      </c>
+      <c r="B6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F6">
+        <v>12118</v>
+      </c>
+      <c r="G6" t="s">
+        <v>25</v>
+      </c>
+      <c r="H6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>26</v>
+      </c>
+      <c r="B7" t="s">
+        <v>27</v>
+      </c>
+      <c r="C7" t="s">
+        <v>10</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F7">
+        <v>10572</v>
+      </c>
+      <c r="G7" t="s">
+        <v>28</v>
+      </c>
+      <c r="H7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>29</v>
+      </c>
+      <c r="B8" t="s">
+        <v>30</v>
+      </c>
+      <c r="C8" t="s">
+        <v>10</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E8" t="s">
+        <v>12</v>
+      </c>
+      <c r="F8">
+        <v>10030</v>
+      </c>
+      <c r="G8" t="s">
+        <v>31</v>
+      </c>
+      <c r="H8" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>32</v>
+      </c>
+      <c r="B9" t="s">
+        <v>33</v>
+      </c>
+      <c r="C9" t="s">
+        <v>10</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E9" t="s">
+        <v>12</v>
+      </c>
+      <c r="F9">
+        <v>10615</v>
+      </c>
+      <c r="G9" t="s">
+        <v>34</v>
+      </c>
+      <c r="H9" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>35</v>
+      </c>
+      <c r="B10" t="s">
+        <v>36</v>
+      </c>
+      <c r="C10" t="s">
+        <v>10</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E10" t="s">
+        <v>12</v>
+      </c>
+      <c r="F10">
+        <v>9661</v>
+      </c>
+      <c r="G10" t="s">
+        <v>37</v>
+      </c>
+      <c r="H10" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>38</v>
+      </c>
+      <c r="B11" t="s">
+        <v>39</v>
+      </c>
+      <c r="C11" t="s">
+        <v>10</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E11" t="s">
+        <v>12</v>
+      </c>
+      <c r="F11">
+        <v>7201</v>
+      </c>
+      <c r="G11" t="s">
+        <v>40</v>
+      </c>
+      <c r="H11" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>41</v>
+      </c>
+      <c r="B12" t="s">
+        <v>42</v>
+      </c>
+      <c r="C12" t="s">
+        <v>10</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E12" t="s">
+        <v>12</v>
+      </c>
+      <c r="F12">
+        <v>10021</v>
+      </c>
+      <c r="G12" t="s">
+        <v>43</v>
+      </c>
+      <c r="H12" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>44</v>
+      </c>
+      <c r="B13" t="s">
+        <v>45</v>
+      </c>
+      <c r="C13" t="s">
+        <v>10</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E13" t="s">
+        <v>12</v>
+      </c>
+      <c r="F13">
+        <v>12509</v>
+      </c>
+      <c r="G13" t="s">
+        <v>46</v>
+      </c>
+      <c r="H13" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>47</v>
+      </c>
+      <c r="B14" t="s">
+        <v>48</v>
+      </c>
+      <c r="C14" t="s">
+        <v>10</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E14" t="s">
+        <v>12</v>
+      </c>
+      <c r="F14">
+        <v>9747</v>
+      </c>
+      <c r="G14" t="s">
+        <v>49</v>
+      </c>
+      <c r="H14" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>50</v>
+      </c>
+      <c r="B15" t="s">
+        <v>51</v>
+      </c>
+      <c r="C15" t="s">
+        <v>10</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E15" t="s">
+        <v>12</v>
+      </c>
+      <c r="F15">
+        <v>10198</v>
+      </c>
+      <c r="G15" t="s">
+        <v>52</v>
+      </c>
+      <c r="H15" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>53</v>
+      </c>
+      <c r="B16" t="s">
+        <v>54</v>
+      </c>
+      <c r="C16" t="s">
+        <v>10</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E16" t="s">
+        <v>12</v>
+      </c>
+      <c r="F16">
+        <v>11573</v>
+      </c>
+      <c r="G16" t="s">
+        <v>55</v>
+      </c>
+      <c r="H16" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>56</v>
+      </c>
+      <c r="B17" t="s">
+        <v>57</v>
+      </c>
+      <c r="C17" t="s">
+        <v>58</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E17" t="s">
+        <v>12</v>
+      </c>
+      <c r="F17">
+        <v>13384</v>
+      </c>
+      <c r="G17" t="s">
+        <v>59</v>
+      </c>
+      <c r="H17" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>60</v>
+      </c>
+      <c r="B18" t="s">
+        <v>61</v>
+      </c>
+      <c r="C18" t="s">
+        <v>58</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E18" t="s">
+        <v>12</v>
+      </c>
+      <c r="F18">
+        <v>13827</v>
+      </c>
+      <c r="G18" t="s">
+        <v>62</v>
+      </c>
+      <c r="H18" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>63</v>
+      </c>
+      <c r="B19" t="s">
+        <v>64</v>
+      </c>
+      <c r="C19" t="s">
+        <v>58</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E19" t="s">
+        <v>12</v>
+      </c>
+      <c r="F19">
+        <v>14983</v>
+      </c>
+      <c r="G19" t="s">
+        <v>65</v>
+      </c>
+      <c r="H19" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>66</v>
+      </c>
+      <c r="B20" t="s">
+        <v>67</v>
+      </c>
+      <c r="C20" t="s">
+        <v>58</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E20" t="s">
+        <v>12</v>
+      </c>
+      <c r="F20">
+        <v>14161</v>
+      </c>
+      <c r="G20" t="s">
+        <v>68</v>
+      </c>
+      <c r="H20" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>69</v>
+      </c>
+      <c r="B21" t="s">
+        <v>70</v>
+      </c>
+      <c r="C21" t="s">
+        <v>58</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E21" t="s">
+        <v>12</v>
+      </c>
+      <c r="F21">
+        <v>17738</v>
+      </c>
+      <c r="G21" t="s">
+        <v>71</v>
+      </c>
+      <c r="H21" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>72</v>
+      </c>
+      <c r="B22" t="s">
+        <v>73</v>
+      </c>
+      <c r="C22" t="s">
+        <v>58</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E22" t="s">
+        <v>12</v>
+      </c>
+      <c r="F22">
+        <v>16376</v>
+      </c>
+      <c r="G22" t="s">
+        <v>74</v>
+      </c>
+      <c r="H22" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>75</v>
+      </c>
+      <c r="B23" t="s">
+        <v>76</v>
+      </c>
+      <c r="C23" t="s">
+        <v>58</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E23" t="s">
+        <v>12</v>
+      </c>
+      <c r="F23">
+        <v>18464</v>
+      </c>
+      <c r="G23" t="s">
+        <v>77</v>
+      </c>
+      <c r="H23" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>78</v>
+      </c>
+      <c r="B24" t="s">
+        <v>79</v>
+      </c>
+      <c r="C24" t="s">
+        <v>58</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E24" t="s">
+        <v>12</v>
+      </c>
+      <c r="F24">
+        <v>11461</v>
+      </c>
+      <c r="G24" t="s">
+        <v>80</v>
+      </c>
+      <c r="H24" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>81</v>
+      </c>
+      <c r="B25" t="s">
+        <v>82</v>
+      </c>
+      <c r="C25" t="s">
+        <v>58</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E25" t="s">
+        <v>12</v>
+      </c>
+      <c r="F25">
+        <v>14463</v>
+      </c>
+      <c r="G25" t="s">
+        <v>83</v>
+      </c>
+      <c r="H25" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>84</v>
+      </c>
+      <c r="B26" t="s">
+        <v>85</v>
+      </c>
+      <c r="C26" t="s">
+        <v>58</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E26" t="s">
+        <v>12</v>
+      </c>
+      <c r="F26">
+        <v>14328</v>
+      </c>
+      <c r="G26" t="s">
+        <v>86</v>
+      </c>
+      <c r="H26" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>87</v>
+      </c>
+      <c r="B27" t="s">
+        <v>88</v>
+      </c>
+      <c r="C27" t="s">
+        <v>58</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E27" t="s">
+        <v>12</v>
+      </c>
+      <c r="F27">
+        <v>14115</v>
+      </c>
+      <c r="G27" t="s">
+        <v>89</v>
+      </c>
+      <c r="H27" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>90</v>
+      </c>
+      <c r="B28" t="s">
+        <v>91</v>
+      </c>
+      <c r="C28" t="s">
+        <v>58</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E28" t="s">
+        <v>12</v>
+      </c>
+      <c r="F28">
+        <v>6218</v>
+      </c>
+      <c r="G28" t="s">
+        <v>92</v>
+      </c>
+      <c r="H28" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>93</v>
+      </c>
+      <c r="B29" t="s">
+        <v>94</v>
+      </c>
+      <c r="C29" t="s">
+        <v>58</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E29" t="s">
+        <v>12</v>
+      </c>
+      <c r="F29">
+        <v>11241</v>
+      </c>
+      <c r="G29" t="s">
+        <v>95</v>
+      </c>
+      <c r="H29" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>96</v>
+      </c>
+      <c r="B30" t="s">
+        <v>97</v>
+      </c>
+      <c r="C30" t="s">
+        <v>58</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E30" t="s">
+        <v>12</v>
+      </c>
+      <c r="F30">
+        <v>6092</v>
+      </c>
+      <c r="G30" t="s">
+        <v>98</v>
+      </c>
+      <c r="H30" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>99</v>
+      </c>
+      <c r="B31" t="s">
+        <v>100</v>
+      </c>
+      <c r="C31" t="s">
+        <v>58</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E31" t="s">
+        <v>12</v>
+      </c>
+      <c r="F31">
+        <v>10013</v>
+      </c>
+      <c r="G31" t="s">
+        <v>101</v>
+      </c>
+      <c r="H31" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>102</v>
+      </c>
+      <c r="B32" t="s">
+        <v>103</v>
+      </c>
+      <c r="C32" t="s">
+        <v>10</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E32" t="s">
+        <v>12</v>
+      </c>
+      <c r="F32">
+        <v>8018</v>
+      </c>
+      <c r="G32" t="s">
+        <v>104</v>
+      </c>
+      <c r="H32" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>105</v>
+      </c>
+      <c r="B33" t="s">
+        <v>106</v>
+      </c>
+      <c r="C33" t="s">
+        <v>10</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E33" t="s">
+        <v>12</v>
+      </c>
+      <c r="F33">
+        <v>6824</v>
+      </c>
+      <c r="G33" t="s">
+        <v>107</v>
+      </c>
+      <c r="H33" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>108</v>
+      </c>
+      <c r="B34" t="s">
+        <v>109</v>
+      </c>
+      <c r="C34" t="s">
+        <v>10</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E34" t="s">
+        <v>12</v>
+      </c>
+      <c r="F34">
+        <v>10785</v>
+      </c>
+      <c r="G34" t="s">
+        <v>110</v>
+      </c>
+      <c r="H34" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>111</v>
+      </c>
+      <c r="B35" t="s">
+        <v>112</v>
+      </c>
+      <c r="C35" t="s">
+        <v>10</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E35" t="s">
+        <v>12</v>
+      </c>
+      <c r="F35">
+        <v>8206</v>
+      </c>
+      <c r="G35" t="s">
+        <v>113</v>
+      </c>
+      <c r="H35" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>114</v>
+      </c>
+      <c r="B36" t="s">
+        <v>115</v>
+      </c>
+      <c r="C36" t="s">
+        <v>10</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E36" t="s">
+        <v>12</v>
+      </c>
+      <c r="F36">
+        <v>11506</v>
+      </c>
+      <c r="G36" t="s">
+        <v>116</v>
+      </c>
+      <c r="H36" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>117</v>
+      </c>
+      <c r="B37" t="s">
+        <v>118</v>
+      </c>
+      <c r="C37" t="s">
+        <v>10</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E37" t="s">
+        <v>12</v>
+      </c>
+      <c r="F37">
+        <v>10170</v>
+      </c>
+      <c r="G37" t="s">
+        <v>119</v>
+      </c>
+      <c r="H37" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>120</v>
+      </c>
+      <c r="B38" t="s">
+        <v>121</v>
+      </c>
+      <c r="C38" t="s">
+        <v>10</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E38" t="s">
+        <v>12</v>
+      </c>
+      <c r="F38">
+        <v>8006</v>
+      </c>
+      <c r="G38" t="s">
+        <v>122</v>
+      </c>
+      <c r="H38" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>123</v>
+      </c>
+      <c r="B39" t="s">
+        <v>124</v>
+      </c>
+      <c r="C39" t="s">
+        <v>10</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E39" t="s">
+        <v>12</v>
+      </c>
+      <c r="F39">
+        <v>7817</v>
+      </c>
+      <c r="G39" t="s">
+        <v>125</v>
+      </c>
+      <c r="H39" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>126</v>
+      </c>
+      <c r="B40" t="s">
+        <v>127</v>
+      </c>
+      <c r="C40" t="s">
+        <v>10</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E40" t="s">
+        <v>12</v>
+      </c>
+      <c r="F40">
+        <v>10326</v>
+      </c>
+      <c r="G40" t="s">
+        <v>128</v>
+      </c>
+      <c r="H40" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>129</v>
+      </c>
+      <c r="B41" t="s">
+        <v>130</v>
+      </c>
+      <c r="C41" t="s">
+        <v>10</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E41" t="s">
+        <v>12</v>
+      </c>
+      <c r="F41">
+        <v>7892</v>
+      </c>
+      <c r="G41" t="s">
+        <v>131</v>
+      </c>
+      <c r="H41" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>132</v>
+      </c>
+      <c r="B42" t="s">
+        <v>133</v>
+      </c>
+      <c r="C42" t="s">
+        <v>10</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E42" t="s">
+        <v>12</v>
+      </c>
+      <c r="F42">
+        <v>11150</v>
+      </c>
+      <c r="G42" t="s">
+        <v>134</v>
+      </c>
+      <c r="H42" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>135</v>
+      </c>
+      <c r="B43" t="s">
+        <v>136</v>
+      </c>
+      <c r="C43" t="s">
+        <v>10</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E43" t="s">
+        <v>12</v>
+      </c>
+      <c r="F43">
+        <v>7094</v>
+      </c>
+      <c r="G43" t="s">
+        <v>137</v>
+      </c>
+      <c r="H43" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>138</v>
+      </c>
+      <c r="B44" t="s">
+        <v>139</v>
+      </c>
+      <c r="C44" t="s">
+        <v>10</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E44" t="s">
+        <v>12</v>
+      </c>
+      <c r="F44">
+        <v>9738</v>
+      </c>
+      <c r="G44" t="s">
+        <v>140</v>
+      </c>
+      <c r="H44" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>141</v>
+      </c>
+      <c r="B45" t="s">
+        <v>142</v>
+      </c>
+      <c r="C45" t="s">
+        <v>10</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E45" t="s">
+        <v>12</v>
+      </c>
+      <c r="F45">
+        <v>10094</v>
+      </c>
+      <c r="G45" t="s">
+        <v>143</v>
+      </c>
+      <c r="H45" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>144</v>
+      </c>
+      <c r="B46" t="s">
+        <v>145</v>
+      </c>
+      <c r="C46" t="s">
+        <v>10</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E46" t="s">
+        <v>12</v>
+      </c>
+      <c r="F46">
+        <v>13855</v>
+      </c>
+      <c r="G46" t="s">
+        <v>146</v>
+      </c>
+      <c r="H46" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>147</v>
+      </c>
+      <c r="B47" t="s">
+        <v>148</v>
+      </c>
+      <c r="C47" t="s">
+        <v>10</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E47" t="s">
+        <v>12</v>
+      </c>
+      <c r="F47">
+        <v>6865</v>
+      </c>
+      <c r="G47" t="s">
+        <v>149</v>
+      </c>
+      <c r="H47" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>150</v>
+      </c>
+      <c r="B48" t="s">
+        <v>151</v>
+      </c>
+      <c r="C48" t="s">
+        <v>10</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E48" t="s">
+        <v>12</v>
+      </c>
+      <c r="F48">
+        <v>11762</v>
+      </c>
+      <c r="G48" t="s">
+        <v>152</v>
+      </c>
+      <c r="H48" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>153</v>
+      </c>
+      <c r="B49" t="s">
+        <v>154</v>
+      </c>
+      <c r="C49" t="s">
+        <v>10</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E49" t="s">
+        <v>12</v>
+      </c>
+      <c r="F49">
+        <v>10275</v>
+      </c>
+      <c r="G49" t="s">
+        <v>155</v>
+      </c>
+      <c r="H49" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>156</v>
+      </c>
+      <c r="B50" t="s">
+        <v>157</v>
+      </c>
+      <c r="C50" t="s">
+        <v>10</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E50" t="s">
+        <v>12</v>
+      </c>
+      <c r="F50">
+        <v>11217</v>
+      </c>
+      <c r="G50" t="s">
+        <v>158</v>
+      </c>
+      <c r="H50" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>159</v>
+      </c>
+      <c r="B51" t="s">
+        <v>160</v>
+      </c>
+      <c r="C51" t="s">
+        <v>10</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E51" t="s">
+        <v>12</v>
+      </c>
+      <c r="F51">
+        <v>10583</v>
+      </c>
+      <c r="G51" t="s">
+        <v>161</v>
+      </c>
+      <c r="H51" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>162</v>
+      </c>
+      <c r="B52" t="s">
+        <v>163</v>
+      </c>
+      <c r="C52" t="s">
+        <v>10</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E52" t="s">
+        <v>12</v>
+      </c>
+      <c r="F52">
+        <v>14941</v>
+      </c>
+      <c r="G52" t="s">
+        <v>164</v>
+      </c>
+      <c r="H52" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>165</v>
+      </c>
+      <c r="B53" t="s">
+        <v>166</v>
+      </c>
+      <c r="C53" t="s">
+        <v>10</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E53" t="s">
+        <v>12</v>
+      </c>
+      <c r="F53">
+        <v>12191</v>
+      </c>
+      <c r="G53" t="s">
+        <v>167</v>
+      </c>
+      <c r="H53" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>168</v>
+      </c>
+      <c r="B54" t="s">
+        <v>169</v>
+      </c>
+      <c r="C54" t="s">
+        <v>10</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E54" t="s">
+        <v>12</v>
+      </c>
+      <c r="F54">
+        <v>13533</v>
+      </c>
+      <c r="G54" t="s">
+        <v>170</v>
+      </c>
+      <c r="H54" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>171</v>
+      </c>
+      <c r="B55" t="s">
+        <v>172</v>
+      </c>
+      <c r="C55" t="s">
+        <v>10</v>
+      </c>
+      <c r="D55" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E55" t="s">
+        <v>12</v>
+      </c>
+      <c r="F55">
+        <v>8971</v>
+      </c>
+      <c r="G55" t="s">
+        <v>173</v>
+      </c>
+      <c r="H55" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>174</v>
+      </c>
+      <c r="B56" t="s">
+        <v>175</v>
+      </c>
+      <c r="C56" t="s">
+        <v>10</v>
+      </c>
+      <c r="D56" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E56" t="s">
+        <v>12</v>
+      </c>
+      <c r="F56">
+        <v>9918</v>
+      </c>
+      <c r="G56" t="s">
+        <v>176</v>
+      </c>
+      <c r="H56" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>177</v>
+      </c>
+      <c r="B57" t="s">
+        <v>178</v>
+      </c>
+      <c r="C57" t="s">
+        <v>10</v>
+      </c>
+      <c r="D57" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E57" t="s">
+        <v>12</v>
+      </c>
+      <c r="F57">
+        <v>5592</v>
+      </c>
+      <c r="G57" t="s">
+        <v>179</v>
+      </c>
+      <c r="H57" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>180</v>
+      </c>
+      <c r="B58" t="s">
+        <v>181</v>
+      </c>
+      <c r="C58" t="s">
+        <v>10</v>
+      </c>
+      <c r="D58" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E58" t="s">
+        <v>12</v>
+      </c>
+      <c r="F58">
+        <v>4431</v>
+      </c>
+      <c r="G58" t="s">
+        <v>182</v>
+      </c>
+      <c r="H58" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>183</v>
+      </c>
+      <c r="B59" t="s">
+        <v>184</v>
+      </c>
+      <c r="C59" t="s">
+        <v>10</v>
+      </c>
+      <c r="D59" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E59" t="s">
+        <v>12</v>
+      </c>
+      <c r="F59">
+        <v>4501</v>
+      </c>
+      <c r="G59" t="s">
+        <v>185</v>
+      </c>
+      <c r="H59" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>186</v>
+      </c>
+      <c r="B60" t="s">
+        <v>187</v>
+      </c>
+      <c r="C60" t="s">
+        <v>10</v>
+      </c>
+      <c r="D60" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E60" t="s">
+        <v>12</v>
+      </c>
+      <c r="F60">
+        <v>4739</v>
+      </c>
+      <c r="G60" t="s">
+        <v>188</v>
+      </c>
+      <c r="H60" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>189</v>
+      </c>
+      <c r="B61" t="s">
+        <v>190</v>
+      </c>
+      <c r="C61" t="s">
+        <v>10</v>
+      </c>
+      <c r="D61" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E61" t="s">
+        <v>12</v>
+      </c>
+      <c r="F61">
+        <v>4402</v>
+      </c>
+      <c r="G61" t="s">
+        <v>191</v>
+      </c>
+      <c r="H61" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>192</v>
+      </c>
+      <c r="B62" t="s">
+        <v>193</v>
+      </c>
+      <c r="C62" t="s">
+        <v>194</v>
+      </c>
+      <c r="D62" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E62" t="s">
+        <v>12</v>
+      </c>
+      <c r="F62">
+        <v>8612</v>
+      </c>
+      <c r="G62" t="s">
+        <v>195</v>
+      </c>
+      <c r="H62" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>196</v>
+      </c>
+      <c r="B63" t="s">
+        <v>197</v>
+      </c>
+      <c r="C63" t="s">
+        <v>194</v>
+      </c>
+      <c r="D63" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E63" t="s">
+        <v>12</v>
+      </c>
+      <c r="F63">
+        <v>6321</v>
+      </c>
+      <c r="G63" t="s">
+        <v>198</v>
+      </c>
+      <c r="H63" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>199</v>
+      </c>
+      <c r="B64" t="s">
+        <v>200</v>
+      </c>
+      <c r="C64" t="s">
+        <v>194</v>
+      </c>
+      <c r="D64" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E64" t="s">
+        <v>12</v>
+      </c>
+      <c r="F64">
+        <v>7140</v>
+      </c>
+      <c r="G64" t="s">
+        <v>201</v>
+      </c>
+      <c r="H64" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>202</v>
+      </c>
+      <c r="B65" t="s">
+        <v>203</v>
+      </c>
+      <c r="C65" t="s">
+        <v>194</v>
+      </c>
+      <c r="D65" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E65" t="s">
+        <v>12</v>
+      </c>
+      <c r="F65">
+        <v>7826</v>
+      </c>
+      <c r="G65" t="s">
+        <v>204</v>
+      </c>
+      <c r="H65" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>205</v>
+      </c>
+      <c r="B66" t="s">
+        <v>206</v>
+      </c>
+      <c r="C66" t="s">
+        <v>194</v>
+      </c>
+      <c r="D66" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E66" t="s">
+        <v>12</v>
+      </c>
+      <c r="F66">
+        <v>7548</v>
+      </c>
+      <c r="G66" t="s">
+        <v>207</v>
+      </c>
+      <c r="H66" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>208</v>
+      </c>
+      <c r="B67" t="s">
+        <v>209</v>
+      </c>
+      <c r="C67" t="s">
+        <v>194</v>
+      </c>
+      <c r="D67" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E67" t="s">
+        <v>12</v>
+      </c>
+      <c r="F67">
+        <v>10820</v>
+      </c>
+      <c r="G67" t="s">
+        <v>210</v>
+      </c>
+      <c r="H67" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>211</v>
+      </c>
+      <c r="B68" t="s">
+        <v>212</v>
+      </c>
+      <c r="C68" t="s">
+        <v>194</v>
+      </c>
+      <c r="D68" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E68" t="s">
+        <v>12</v>
+      </c>
+      <c r="F68">
+        <v>12059</v>
+      </c>
+      <c r="G68" t="s">
+        <v>213</v>
+      </c>
+      <c r="H68" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>214</v>
+      </c>
+      <c r="B69" t="s">
+        <v>215</v>
+      </c>
+      <c r="C69" t="s">
+        <v>194</v>
+      </c>
+      <c r="D69" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E69" t="s">
+        <v>12</v>
+      </c>
+      <c r="F69">
+        <v>11945</v>
+      </c>
+      <c r="G69" t="s">
+        <v>216</v>
+      </c>
+      <c r="H69" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>217</v>
+      </c>
+      <c r="B70" t="s">
+        <v>218</v>
+      </c>
+      <c r="C70" t="s">
+        <v>194</v>
+      </c>
+      <c r="D70" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E70" t="s">
+        <v>12</v>
+      </c>
+      <c r="F70">
+        <v>12443</v>
+      </c>
+      <c r="G70" t="s">
+        <v>219</v>
+      </c>
+      <c r="H70" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>220</v>
+      </c>
+      <c r="B71" t="s">
+        <v>221</v>
+      </c>
+      <c r="C71" t="s">
+        <v>194</v>
+      </c>
+      <c r="D71" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E71" t="s">
+        <v>12</v>
+      </c>
+      <c r="F71">
+        <v>13327</v>
+      </c>
+      <c r="G71" t="s">
+        <v>222</v>
+      </c>
+      <c r="H71" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>223</v>
+      </c>
+      <c r="B72" t="s">
+        <v>224</v>
+      </c>
+      <c r="C72" t="s">
+        <v>194</v>
+      </c>
+      <c r="D72" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E72" t="s">
+        <v>12</v>
+      </c>
+      <c r="F72">
+        <v>12997</v>
+      </c>
+      <c r="G72" t="s">
+        <v>225</v>
+      </c>
+      <c r="H72" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>226</v>
+      </c>
+      <c r="B73" t="s">
+        <v>227</v>
+      </c>
+      <c r="C73" t="s">
+        <v>194</v>
+      </c>
+      <c r="D73" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E73" t="s">
+        <v>12</v>
+      </c>
+      <c r="F73">
+        <v>10244</v>
+      </c>
+      <c r="G73" t="s">
+        <v>228</v>
+      </c>
+      <c r="H73" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>229</v>
+      </c>
+      <c r="B74" t="s">
+        <v>230</v>
+      </c>
+      <c r="C74" t="s">
+        <v>194</v>
+      </c>
+      <c r="D74" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E74" t="s">
+        <v>12</v>
+      </c>
+      <c r="F74">
+        <v>10480</v>
+      </c>
+      <c r="G74" t="s">
+        <v>231</v>
+      </c>
+      <c r="H74" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>232</v>
+      </c>
+      <c r="B75" t="s">
+        <v>233</v>
+      </c>
+      <c r="C75" t="s">
+        <v>194</v>
+      </c>
+      <c r="D75" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E75" t="s">
+        <v>12</v>
+      </c>
+      <c r="F75">
+        <v>11396</v>
+      </c>
+      <c r="G75" t="s">
+        <v>234</v>
+      </c>
+      <c r="H75" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>235</v>
+      </c>
+      <c r="B76" t="s">
+        <v>236</v>
+      </c>
+      <c r="C76" t="s">
+        <v>194</v>
+      </c>
+      <c r="D76" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E76" t="s">
+        <v>12</v>
+      </c>
+      <c r="F76">
+        <v>8317</v>
+      </c>
+      <c r="G76" t="s">
+        <v>237</v>
+      </c>
+      <c r="H76" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>238</v>
+      </c>
+      <c r="B77" t="s">
+        <v>239</v>
+      </c>
+      <c r="C77" t="s">
+        <v>240</v>
+      </c>
+      <c r="D77" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E77" t="s">
+        <v>12</v>
+      </c>
+      <c r="F77">
+        <v>8916</v>
+      </c>
+      <c r="G77" t="s">
+        <v>241</v>
+      </c>
+      <c r="H77" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>242</v>
+      </c>
+      <c r="B78" t="s">
+        <v>243</v>
+      </c>
+      <c r="C78" t="s">
+        <v>240</v>
+      </c>
+      <c r="D78" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E78" t="s">
+        <v>12</v>
+      </c>
+      <c r="F78">
+        <v>11470</v>
+      </c>
+      <c r="G78" t="s">
+        <v>244</v>
+      </c>
+      <c r="H78" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>245</v>
+      </c>
+      <c r="B79" t="s">
+        <v>246</v>
+      </c>
+      <c r="C79" t="s">
+        <v>240</v>
+      </c>
+      <c r="D79" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E79" t="s">
+        <v>12</v>
+      </c>
+      <c r="F79">
+        <v>10026</v>
+      </c>
+      <c r="G79" t="s">
+        <v>247</v>
+      </c>
+      <c r="H79" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>248</v>
+      </c>
+      <c r="B80" t="s">
+        <v>249</v>
+      </c>
+      <c r="C80" t="s">
+        <v>240</v>
+      </c>
+      <c r="D80" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E80" t="s">
+        <v>12</v>
+      </c>
+      <c r="F80">
+        <v>8338</v>
+      </c>
+      <c r="G80" t="s">
+        <v>250</v>
+      </c>
+      <c r="H80" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>251</v>
+      </c>
+      <c r="B81" t="s">
+        <v>252</v>
+      </c>
+      <c r="C81" t="s">
+        <v>240</v>
+      </c>
+      <c r="D81" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E81" t="s">
+        <v>12</v>
+      </c>
+      <c r="F81">
+        <v>11075</v>
+      </c>
+      <c r="G81" t="s">
+        <v>253</v>
+      </c>
+      <c r="H81" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>254</v>
+      </c>
+      <c r="B82" t="s">
+        <v>255</v>
+      </c>
+      <c r="C82" t="s">
+        <v>240</v>
+      </c>
+      <c r="D82" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E82" t="s">
+        <v>12</v>
+      </c>
+      <c r="F82">
+        <v>11899</v>
+      </c>
+      <c r="G82" t="s">
+        <v>256</v>
+      </c>
+      <c r="H82" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>257</v>
+      </c>
+      <c r="B83" t="s">
+        <v>258</v>
+      </c>
+      <c r="C83" t="s">
+        <v>240</v>
+      </c>
+      <c r="D83" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E83" t="s">
+        <v>12</v>
+      </c>
+      <c r="F83">
+        <v>10475</v>
+      </c>
+      <c r="G83" t="s">
+        <v>259</v>
+      </c>
+      <c r="H83" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>260</v>
+      </c>
+      <c r="B84" t="s">
+        <v>261</v>
+      </c>
+      <c r="C84" t="s">
+        <v>240</v>
+      </c>
+      <c r="D84" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E84" t="s">
+        <v>12</v>
+      </c>
+      <c r="F84">
+        <v>12523</v>
+      </c>
+      <c r="G84" t="s">
+        <v>262</v>
+      </c>
+      <c r="H84" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>263</v>
+      </c>
+      <c r="B85" t="s">
+        <v>264</v>
+      </c>
+      <c r="C85" t="s">
+        <v>240</v>
+      </c>
+      <c r="D85" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E85" t="s">
+        <v>12</v>
+      </c>
+      <c r="F85">
+        <v>14679</v>
+      </c>
+      <c r="G85" t="s">
+        <v>265</v>
+      </c>
+      <c r="H85" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>266</v>
+      </c>
+      <c r="B86" t="s">
+        <v>267</v>
+      </c>
+      <c r="C86" t="s">
+        <v>240</v>
+      </c>
+      <c r="D86" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E86" t="s">
+        <v>12</v>
+      </c>
+      <c r="F86">
+        <v>15350</v>
+      </c>
+      <c r="G86" t="s">
+        <v>268</v>
+      </c>
+      <c r="H86" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>269</v>
+      </c>
+      <c r="B87" t="s">
+        <v>270</v>
+      </c>
+      <c r="C87" t="s">
+        <v>240</v>
+      </c>
+      <c r="D87" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E87" t="s">
+        <v>12</v>
+      </c>
+      <c r="F87">
+        <v>17040</v>
+      </c>
+      <c r="G87" t="s">
+        <v>271</v>
+      </c>
+      <c r="H87" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>272</v>
+      </c>
+      <c r="B88" t="s">
+        <v>273</v>
+      </c>
+      <c r="C88" t="s">
+        <v>240</v>
+      </c>
+      <c r="D88" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E88" t="s">
+        <v>12</v>
+      </c>
+      <c r="F88">
+        <v>18350</v>
+      </c>
+      <c r="G88" t="s">
+        <v>274</v>
+      </c>
+      <c r="H88" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>275</v>
+      </c>
+      <c r="B89" t="s">
+        <v>276</v>
+      </c>
+      <c r="C89" t="s">
+        <v>240</v>
+      </c>
+      <c r="D89" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E89" t="s">
+        <v>12</v>
+      </c>
+      <c r="F89">
+        <v>18851</v>
+      </c>
+      <c r="G89" t="s">
+        <v>277</v>
+      </c>
+      <c r="H89" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>278</v>
+      </c>
+      <c r="B90" t="s">
+        <v>279</v>
+      </c>
+      <c r="C90" t="s">
+        <v>240</v>
+      </c>
+      <c r="D90" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E90" t="s">
+        <v>12</v>
+      </c>
+      <c r="F90">
+        <v>17360</v>
+      </c>
+      <c r="G90" t="s">
+        <v>280</v>
+      </c>
+      <c r="H90" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>281</v>
+      </c>
+      <c r="B91" t="s">
+        <v>282</v>
+      </c>
+      <c r="C91" t="s">
+        <v>240</v>
+      </c>
+      <c r="D91" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E91" t="s">
+        <v>12</v>
+      </c>
+      <c r="F91">
+        <v>20118</v>
+      </c>
+      <c r="G91" t="s">
+        <v>283</v>
+      </c>
+      <c r="H91" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>284</v>
+      </c>
+      <c r="B92" t="s">
+        <v>285</v>
+      </c>
+      <c r="C92" t="s">
+        <v>286</v>
+      </c>
+      <c r="D92" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E92" t="s">
+        <v>12</v>
+      </c>
+      <c r="F92">
+        <v>14139</v>
+      </c>
+      <c r="G92" t="s">
+        <v>287</v>
+      </c>
+      <c r="H92" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>288</v>
+      </c>
+      <c r="B93" t="s">
+        <v>289</v>
+      </c>
+      <c r="C93" t="s">
+        <v>286</v>
+      </c>
+      <c r="D93" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E93" t="s">
+        <v>12</v>
+      </c>
+      <c r="F93">
+        <v>8797</v>
+      </c>
+      <c r="G93" t="s">
+        <v>290</v>
+      </c>
+      <c r="H93" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>291</v>
+      </c>
+      <c r="B94" t="s">
+        <v>292</v>
+      </c>
+      <c r="C94" t="s">
+        <v>286</v>
+      </c>
+      <c r="D94" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E94" t="s">
+        <v>12</v>
+      </c>
+      <c r="F94">
+        <v>8023</v>
+      </c>
+      <c r="G94" t="s">
+        <v>293</v>
+      </c>
+      <c r="H94" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>294</v>
+      </c>
+      <c r="B95" t="s">
+        <v>295</v>
+      </c>
+      <c r="C95" t="s">
+        <v>286</v>
+      </c>
+      <c r="D95" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E95" t="s">
+        <v>12</v>
+      </c>
+      <c r="F95">
+        <v>6381</v>
+      </c>
+      <c r="G95" t="s">
+        <v>296</v>
+      </c>
+      <c r="H95" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>297</v>
+      </c>
+      <c r="B96" t="s">
+        <v>298</v>
+      </c>
+      <c r="C96" t="s">
+        <v>286</v>
+      </c>
+      <c r="D96" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E96" t="s">
+        <v>12</v>
+      </c>
+      <c r="F96">
+        <v>6892</v>
+      </c>
+      <c r="G96" t="s">
+        <v>299</v>
+      </c>
+      <c r="H96" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="97" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>300</v>
+      </c>
+      <c r="B97" t="s">
+        <v>301</v>
+      </c>
+      <c r="C97" t="s">
+        <v>286</v>
+      </c>
+      <c r="D97" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E97" t="s">
+        <v>12</v>
+      </c>
+      <c r="F97">
+        <v>11874</v>
+      </c>
+      <c r="G97" t="s">
+        <v>302</v>
+      </c>
+      <c r="H97" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="98" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>303</v>
+      </c>
+      <c r="B98" t="s">
+        <v>304</v>
+      </c>
+      <c r="C98" t="s">
+        <v>286</v>
+      </c>
+      <c r="D98" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E98" t="s">
+        <v>12</v>
+      </c>
+      <c r="F98">
+        <v>10941</v>
+      </c>
+      <c r="G98" t="s">
+        <v>305</v>
+      </c>
+      <c r="H98" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="99" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>306</v>
+      </c>
+      <c r="B99" t="s">
+        <v>307</v>
+      </c>
+      <c r="C99" t="s">
+        <v>286</v>
+      </c>
+      <c r="D99" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E99" t="s">
+        <v>12</v>
+      </c>
+      <c r="F99">
+        <v>8674</v>
+      </c>
+      <c r="G99" t="s">
+        <v>308</v>
+      </c>
+      <c r="H99" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="100" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>309</v>
+      </c>
+      <c r="B100" t="s">
+        <v>310</v>
+      </c>
+      <c r="C100" t="s">
+        <v>286</v>
+      </c>
+      <c r="D100" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E100" t="s">
+        <v>12</v>
+      </c>
+      <c r="F100">
+        <v>7574</v>
+      </c>
+      <c r="G100" t="s">
+        <v>311</v>
+      </c>
+      <c r="H100" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="101" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>312</v>
+      </c>
+      <c r="B101" t="s">
+        <v>313</v>
+      </c>
+      <c r="C101" t="s">
+        <v>286</v>
+      </c>
+      <c r="D101" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E101" t="s">
+        <v>12</v>
+      </c>
+      <c r="F101">
+        <v>10196</v>
+      </c>
+      <c r="G101" t="s">
+        <v>314</v>
+      </c>
+      <c r="H101" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="102" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>315</v>
+      </c>
+      <c r="B102" t="s">
+        <v>316</v>
+      </c>
+      <c r="C102" t="s">
+        <v>286</v>
+      </c>
+      <c r="D102" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E102" t="s">
+        <v>12</v>
+      </c>
+      <c r="F102">
+        <v>9854</v>
+      </c>
+      <c r="G102" t="s">
+        <v>317</v>
+      </c>
+      <c r="H102" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="103" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>318</v>
+      </c>
+      <c r="B103" t="s">
+        <v>319</v>
+      </c>
+      <c r="C103" t="s">
+        <v>286</v>
+      </c>
+      <c r="D103" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E103" t="s">
+        <v>12</v>
+      </c>
+      <c r="F103">
+        <v>10219</v>
+      </c>
+      <c r="G103" t="s">
+        <v>320</v>
+      </c>
+      <c r="H103" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="104" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>321</v>
+      </c>
+      <c r="B104" t="s">
+        <v>322</v>
+      </c>
+      <c r="C104" t="s">
+        <v>286</v>
+      </c>
+      <c r="D104" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E104" t="s">
+        <v>12</v>
+      </c>
+      <c r="F104">
+        <v>9736</v>
+      </c>
+      <c r="G104" t="s">
+        <v>323</v>
+      </c>
+      <c r="H104" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="105" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>324</v>
+      </c>
+      <c r="B105" t="s">
+        <v>325</v>
+      </c>
+      <c r="C105" t="s">
+        <v>286</v>
+      </c>
+      <c r="D105" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E105" t="s">
+        <v>12</v>
+      </c>
+      <c r="F105">
+        <v>9626</v>
+      </c>
+      <c r="G105" t="s">
+        <v>326</v>
+      </c>
+      <c r="H105" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="106" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>327</v>
+      </c>
+      <c r="B106" t="s">
+        <v>328</v>
+      </c>
+      <c r="C106" t="s">
+        <v>286</v>
+      </c>
+      <c r="D106" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E106" t="s">
+        <v>12</v>
+      </c>
+      <c r="F106">
+        <v>8179</v>
+      </c>
+      <c r="G106" t="s">
+        <v>329</v>
+      </c>
+      <c r="H106" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="107" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>330</v>
+      </c>
+      <c r="B107" t="s">
+        <v>331</v>
+      </c>
+      <c r="C107" t="s">
+        <v>332</v>
+      </c>
+      <c r="D107" s="3" t="s">
+        <v>333</v>
+      </c>
+      <c r="E107" t="s">
+        <v>334</v>
+      </c>
+      <c r="F107">
+        <v>8554</v>
+      </c>
+      <c r="G107" t="s">
+        <v>335</v>
+      </c>
+      <c r="H107" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="108" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
+        <v>336</v>
+      </c>
+      <c r="B108" t="s">
+        <v>337</v>
+      </c>
+      <c r="C108" t="s">
+        <v>332</v>
+      </c>
+      <c r="D108" s="3" t="s">
+        <v>333</v>
+      </c>
+      <c r="E108" t="s">
+        <v>334</v>
+      </c>
+      <c r="F108">
+        <v>10273</v>
+      </c>
+      <c r="G108" t="s">
+        <v>338</v>
+      </c>
+      <c r="H108" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="109" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
+        <v>339</v>
+      </c>
+      <c r="B109" t="s">
+        <v>340</v>
+      </c>
+      <c r="C109" t="s">
+        <v>332</v>
+      </c>
+      <c r="D109" s="3" t="s">
+        <v>333</v>
+      </c>
+      <c r="E109" t="s">
+        <v>334</v>
+      </c>
+      <c r="F109">
+        <v>8548</v>
+      </c>
+      <c r="G109" t="s">
+        <v>341</v>
+      </c>
+      <c r="H109" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="110" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
+        <v>342</v>
+      </c>
+      <c r="B110" t="s">
+        <v>343</v>
+      </c>
+      <c r="C110" t="s">
+        <v>332</v>
+      </c>
+      <c r="D110" s="3" t="s">
+        <v>333</v>
+      </c>
+      <c r="E110" t="s">
+        <v>334</v>
+      </c>
+      <c r="F110">
+        <v>11066</v>
+      </c>
+      <c r="G110" t="s">
+        <v>344</v>
+      </c>
+      <c r="H110" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="111" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
+        <v>345</v>
+      </c>
+      <c r="B111" t="s">
+        <v>346</v>
+      </c>
+      <c r="C111" t="s">
+        <v>332</v>
+      </c>
+      <c r="D111" s="3" t="s">
+        <v>333</v>
+      </c>
+      <c r="E111" t="s">
+        <v>334</v>
+      </c>
+      <c r="F111">
+        <v>10416</v>
+      </c>
+      <c r="G111" t="s">
+        <v>347</v>
+      </c>
+      <c r="H111" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="112" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
+        <v>348</v>
+      </c>
+      <c r="B112" t="s">
+        <v>349</v>
+      </c>
+      <c r="C112" t="s">
+        <v>332</v>
+      </c>
+      <c r="D112" s="3" t="s">
+        <v>333</v>
+      </c>
+      <c r="E112" t="s">
+        <v>334</v>
+      </c>
+      <c r="F112">
+        <v>12277</v>
+      </c>
+      <c r="G112" t="s">
+        <v>350</v>
+      </c>
+      <c r="H112" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="113" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
+        <v>351</v>
+      </c>
+      <c r="B113" t="s">
+        <v>352</v>
+      </c>
+      <c r="C113" t="s">
+        <v>332</v>
+      </c>
+      <c r="D113" s="3" t="s">
+        <v>333</v>
+      </c>
+      <c r="E113" t="s">
+        <v>334</v>
+      </c>
+      <c r="F113">
+        <v>11422</v>
+      </c>
+      <c r="G113" t="s">
+        <v>353</v>
+      </c>
+      <c r="H113" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="114" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A114" t="s">
+        <v>354</v>
+      </c>
+      <c r="B114" t="s">
+        <v>355</v>
+      </c>
+      <c r="C114" t="s">
+        <v>332</v>
+      </c>
+      <c r="D114" s="3" t="s">
+        <v>333</v>
+      </c>
+      <c r="E114" t="s">
+        <v>334</v>
+      </c>
+      <c r="F114">
+        <v>10449</v>
+      </c>
+      <c r="G114" t="s">
+        <v>356</v>
+      </c>
+      <c r="H114" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="115" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A115" t="s">
+        <v>357</v>
+      </c>
+      <c r="B115" t="s">
+        <v>358</v>
+      </c>
+      <c r="C115" t="s">
+        <v>332</v>
+      </c>
+      <c r="D115" s="3" t="s">
+        <v>333</v>
+      </c>
+      <c r="E115" t="s">
+        <v>334</v>
+      </c>
+      <c r="F115">
+        <v>14060</v>
+      </c>
+      <c r="G115" t="s">
+        <v>359</v>
+      </c>
+      <c r="H115" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="116" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A116" t="s">
+        <v>360</v>
+      </c>
+      <c r="B116" t="s">
+        <v>361</v>
+      </c>
+      <c r="C116" t="s">
+        <v>332</v>
+      </c>
+      <c r="D116" s="3" t="s">
+        <v>333</v>
+      </c>
+      <c r="E116" t="s">
+        <v>334</v>
+      </c>
+      <c r="F116">
+        <v>15498</v>
+      </c>
+      <c r="G116" t="s">
+        <v>362</v>
+      </c>
+      <c r="H116" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="117" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A117" t="s">
+        <v>363</v>
+      </c>
+      <c r="B117" t="s">
+        <v>364</v>
+      </c>
+      <c r="C117" t="s">
+        <v>332</v>
+      </c>
+      <c r="D117" s="3" t="s">
+        <v>333</v>
+      </c>
+      <c r="E117" t="s">
+        <v>334</v>
+      </c>
+      <c r="F117">
+        <v>11362</v>
+      </c>
+      <c r="G117" t="s">
+        <v>365</v>
+      </c>
+      <c r="H117" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="118" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A118" t="s">
+        <v>366</v>
+      </c>
+      <c r="B118" t="s">
+        <v>367</v>
+      </c>
+      <c r="C118" t="s">
+        <v>332</v>
+      </c>
+      <c r="D118" s="3" t="s">
+        <v>333</v>
+      </c>
+      <c r="E118" t="s">
+        <v>334</v>
+      </c>
+      <c r="F118">
+        <v>11370</v>
+      </c>
+      <c r="G118" t="s">
+        <v>368</v>
+      </c>
+      <c r="H118" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="119" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A119" t="s">
+        <v>369</v>
+      </c>
+      <c r="B119" t="s">
+        <v>370</v>
+      </c>
+      <c r="C119" t="s">
+        <v>332</v>
+      </c>
+      <c r="D119" s="3" t="s">
+        <v>333</v>
+      </c>
+      <c r="E119" t="s">
+        <v>334</v>
+      </c>
+      <c r="F119">
+        <v>10043</v>
+      </c>
+      <c r="G119" t="s">
+        <v>371</v>
+      </c>
+      <c r="H119" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="120" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A120" t="s">
+        <v>372</v>
+      </c>
+      <c r="B120" t="s">
+        <v>373</v>
+      </c>
+      <c r="C120" t="s">
+        <v>332</v>
+      </c>
+      <c r="D120" s="3" t="s">
+        <v>333</v>
+      </c>
+      <c r="E120" t="s">
+        <v>334</v>
+      </c>
+      <c r="F120">
+        <v>8030</v>
+      </c>
+      <c r="G120" t="s">
+        <v>374</v>
+      </c>
+      <c r="H120" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="121" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A121" t="s">
+        <v>375</v>
+      </c>
+      <c r="B121" t="s">
+        <v>376</v>
+      </c>
+      <c r="C121" t="s">
+        <v>332</v>
+      </c>
+      <c r="D121" s="3" t="s">
+        <v>333</v>
+      </c>
+      <c r="E121" t="s">
+        <v>334</v>
+      </c>
+      <c r="F121">
+        <v>9683</v>
+      </c>
+      <c r="G121" t="s">
+        <v>377</v>
+      </c>
+      <c r="H121" t="s">
+        <v>12</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
